--- a/resource/groundTruths/requirement/CF_M08_ground_truth_requirement.xlsx
+++ b/resource/groundTruths/requirement/CF_M08_ground_truth_requirement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/requirement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E01873E-38F2-D342-9DB5-3807B5C55BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5C227F-D6E2-0D4C-8E36-F0EF1CB83A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7380" yWindow="820" windowWidth="22020" windowHeight="16880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1620" yWindow="920" windowWidth="10000" windowHeight="16880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="125">
   <si>
     <t>Document ID</t>
   </si>
@@ -38,18 +38,12 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>Categorization</t>
-  </si>
-  <si>
     <t>Related to</t>
   </si>
   <si>
     <t>Page Number</t>
   </si>
   <si>
-    <t>Applied Fixes</t>
-  </si>
-  <si>
     <t>CF_M08</t>
   </si>
   <si>
@@ -143,9 +137,6 @@
     <t>QR</t>
   </si>
   <si>
-    <t>Volere</t>
-  </si>
-  <si>
     <t>Criterion</t>
   </si>
   <si>
@@ -402,6 +393,9 @@
   </si>
   <si>
     <t>*CF_M08_C24</t>
+  </si>
+  <si>
+    <t>Fixed Type</t>
   </si>
 </sst>
 </file>
@@ -741,10 +735,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -767,602 +761,581 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="H2">
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3">
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4">
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5">
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6">
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
         <v>21</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7">
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" t="s">
         <v>87</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s">
         <v>88</v>
       </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D23" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23">
         <v>32</v>
       </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" t="s">
+        <v>96</v>
+      </c>
+      <c r="G25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26">
         <v>33</v>
       </c>
-      <c r="C14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" t="s">
         <v>37</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E28" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" t="s">
         <v>38</v>
       </c>
-      <c r="D16" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" t="s">
-        <v>40</v>
-      </c>
-      <c r="H16">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="F29" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" t="s">
         <v>37</v>
       </c>
-      <c r="H17">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" t="s">
-        <v>63</v>
-      </c>
-      <c r="F18" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" t="s">
-        <v>41</v>
-      </c>
-      <c r="G19" t="s">
-        <v>42</v>
-      </c>
-      <c r="H19">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" t="s">
-        <v>40</v>
-      </c>
-      <c r="H20">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" t="s">
-        <v>46</v>
-      </c>
-      <c r="H21">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" t="s">
-        <v>67</v>
-      </c>
-      <c r="H22">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" t="s">
-        <v>41</v>
-      </c>
-      <c r="G23" t="s">
-        <v>92</v>
-      </c>
-      <c r="H23">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="E30" t="s">
+        <v>111</v>
+      </c>
+      <c r="G30">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" t="s">
         <v>99</v>
       </c>
-      <c r="C24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" t="s">
-        <v>69</v>
-      </c>
-      <c r="H24">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" t="s">
-        <v>41</v>
-      </c>
-      <c r="G25" t="s">
-        <v>99</v>
-      </c>
-      <c r="H25">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" t="s">
-        <v>100</v>
-      </c>
-      <c r="C26" t="s">
-        <v>96</v>
-      </c>
-      <c r="D26" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26" t="s">
-        <v>40</v>
-      </c>
-      <c r="H26">
+      <c r="D31" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" t="s">
+        <v>98</v>
+      </c>
+      <c r="G31">
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" t="s">
         <v>55</v>
       </c>
-      <c r="C27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D27" t="s">
-        <v>41</v>
-      </c>
-      <c r="G27" t="s">
-        <v>100</v>
-      </c>
-      <c r="H27">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" t="s">
-        <v>113</v>
-      </c>
-      <c r="F28" t="s">
-        <v>40</v>
-      </c>
-      <c r="H28">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" t="s">
-        <v>41</v>
-      </c>
-      <c r="G29" t="s">
-        <v>51</v>
-      </c>
-      <c r="H29">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" t="s">
-        <v>98</v>
-      </c>
-      <c r="D30" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" t="s">
-        <v>114</v>
-      </c>
-      <c r="F30" t="s">
-        <v>40</v>
-      </c>
-      <c r="H30">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" t="s">
-        <v>102</v>
-      </c>
-      <c r="D31" t="s">
-        <v>41</v>
-      </c>
-      <c r="G31" t="s">
-        <v>101</v>
-      </c>
-      <c r="H31">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" t="s">
-        <v>104</v>
-      </c>
-      <c r="C32" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" t="s">
-        <v>58</v>
-      </c>
-      <c r="H32">
+      <c r="G32">
         <v>31</v>
       </c>
     </row>
@@ -1381,274 +1354,274 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/resource/groundTruths/requirement/CF_M08_ground_truth_requirement.xlsx
+++ b/resource/groundTruths/requirement/CF_M08_ground_truth_requirement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/requirement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5C227F-D6E2-0D4C-8E36-F0EF1CB83A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1479A4E2-5BD4-8745-B30D-C0C0090B9C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1620" yWindow="920" windowWidth="10000" windowHeight="16880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -242,9 +242,6 @@
     <t>Integration</t>
   </si>
   <si>
-    <t>Efficiency (of development)</t>
-  </si>
-  <si>
     <t>Flexibility</t>
   </si>
   <si>
@@ -396,6 +393,9 @@
   </si>
   <si>
     <t>Fixed Type</t>
+  </si>
+  <si>
+    <t>Efficiency</t>
   </si>
 </sst>
 </file>
@@ -761,7 +761,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -871,10 +871,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" t="s">
         <v>84</v>
-      </c>
-      <c r="C8" t="s">
-        <v>85</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1027,10 +1027,10 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
         <v>38</v>
@@ -1127,10 +1127,10 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
         <v>37</v>
@@ -1147,16 +1147,16 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s">
         <v>38</v>
       </c>
       <c r="F23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G23">
         <v>32</v>
@@ -1167,10 +1167,10 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D24" t="s">
         <v>37</v>
@@ -1190,13 +1190,13 @@
         <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s">
         <v>38</v>
       </c>
       <c r="F25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G25">
         <v>32</v>
@@ -1207,10 +1207,10 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s">
         <v>37</v>
@@ -1230,13 +1230,13 @@
         <v>52</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
         <v>38</v>
       </c>
       <c r="F27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G27">
         <v>33</v>
@@ -1256,7 +1256,7 @@
         <v>37</v>
       </c>
       <c r="E28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G28">
         <v>33</v>
@@ -1287,16 +1287,16 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
         <v>37</v>
       </c>
       <c r="E30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G30">
         <v>33</v>
@@ -1310,13 +1310,13 @@
         <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s">
         <v>38</v>
       </c>
       <c r="F31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G31">
         <v>33</v>
@@ -1327,7 +1327,7 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
         <v>54</v>
@@ -1368,7 +1368,7 @@
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1379,7 +1379,7 @@
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1390,7 +1390,7 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1401,7 +1401,7 @@
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1412,7 +1412,7 @@
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1423,7 +1423,7 @@
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1431,10 +1431,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1442,10 +1442,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1453,7 +1453,7 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s">
         <v>59</v>
@@ -1464,7 +1464,7 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
         <v>61</v>
@@ -1475,7 +1475,7 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
         <v>63</v>
@@ -1486,7 +1486,7 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
         <v>65</v>
@@ -1497,7 +1497,7 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
         <v>67</v>
@@ -1508,7 +1508,7 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
         <v>69</v>
@@ -1519,7 +1519,7 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
         <v>70</v>
@@ -1530,7 +1530,7 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s">
         <v>71</v>
@@ -1541,7 +1541,7 @@
         <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C31" t="s">
         <v>72</v>
@@ -1552,10 +1552,10 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1563,10 +1563,10 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1574,10 +1574,10 @@
         <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1585,10 +1585,10 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -1596,10 +1596,10 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -1607,10 +1607,10 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -1618,10 +1618,10 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
